--- a/offers/عروض لاكتونيك.xlsx
+++ b/offers/عروض لاكتونيك.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YAHAY ZAQZOUQ\IMPORTANT\ملفات العروض\8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42021ACF-4965-430E-A965-2E77005F4B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108F0719-8817-4CB6-BAAA-8C5C8F22D513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,9 +46,6 @@
     <t>لاكتونيك رقم (1) 800 جرام</t>
   </si>
   <si>
-    <t>2+1</t>
-  </si>
-  <si>
     <t>لاكتونيك رقم (3) 1200 جرام</t>
   </si>
   <si>
@@ -65,6 +62,9 @@
   </si>
   <si>
     <t>00040360</t>
+  </si>
+  <si>
+    <t>1+2</t>
   </si>
 </sst>
 </file>
@@ -531,7 +531,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
@@ -540,7 +540,7 @@
         <v>80.8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E2" s="4">
         <v>46277</v>
@@ -549,21 +549,21 @@
         <v>46249</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3">
         <v>110.4</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E3" s="4">
         <v>46277</v>
@@ -572,21 +572,21 @@
         <v>46249</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3">
         <v>125.42</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E4" s="4">
         <v>46277</v>
@@ -595,7 +595,7 @@
         <v>46249</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
